--- a/karkard/output/کارکرد-مرداد-1405.xlsx
+++ b/karkard/output/کارکرد-مرداد-1405.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,43 +31,49 @@
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="001F4E5F"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="B Nazanin"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="B Nazanin"/>
-      <color rgb="001F4E5F"/>
+      <color rgb="00404040"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
-      <sz val="12"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <color rgb="00595959"/>
-      <sz val="12"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="001F4E5F"/>
-      <sz val="13"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,37 +82,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E5F"/>
+        <fgColor rgb="00404040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF1FA"/>
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF4EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,149 +121,149 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E5F"/>
+        <color rgb="00404040"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -273,7 +274,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -294,13 +295,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -312,13 +313,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -330,13 +331,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +705,15 @@
   <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="95" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8.5" customWidth="1" min="3" max="3"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="8.5" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>بسمه تعالی</t>
@@ -727,7 +725,7 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>فرم ثبت شرح فعالیت روزانه نیروهای خرید خدمت مرکز فضای مجازی بسیج استان اصفهان</t>
@@ -739,7 +737,7 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>با احترام، بدینوسیله کارکرد برادر محسن ابوطالبیان در مرداد ماه ۱۴۰۵ بر اساس جدول ذیل حضورتان ارسال می‌گردد:</t>
@@ -751,7 +749,7 @@
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
     </row>
-    <row r="4" ht="6" customHeight="1">
+    <row r="4" ht="3" customHeight="1">
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
@@ -759,7 +757,7 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
     </row>
-    <row r="5" ht="50" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>ایام ماه</t>
@@ -791,7 +789,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6" ht="25" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>۱</t>
@@ -823,7 +821,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>۲</t>
@@ -843,7 +841,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>۳</t>
@@ -875,7 +873,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>۴</t>
@@ -907,7 +905,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
+    <row r="10" ht="25" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>۵</t>
@@ -939,7 +937,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
+    <row r="11" ht="25" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>۶</t>
@@ -971,7 +969,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" ht="25" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
           <t>۷</t>
@@ -1003,7 +1001,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
+    <row r="13" ht="25" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>۸</t>
@@ -1035,7 +1033,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
           <t>۹</t>
@@ -1067,7 +1065,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1">
+    <row r="15" ht="25" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>۱۰</t>
@@ -1099,7 +1097,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
+    <row r="16" ht="25" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>۱۱</t>
@@ -1131,7 +1129,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
+    <row r="17" ht="25" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
           <t>۱۲</t>
@@ -1163,7 +1161,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>۱۳</t>
@@ -1183,7 +1181,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1">
+    <row r="19" ht="25" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>۱۴</t>
@@ -1215,7 +1213,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
+    <row r="20" ht="25" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
           <t>۱۵</t>
@@ -1247,7 +1245,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
+    <row r="21" ht="16" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
         <is>
           <t>۱۶</t>
@@ -1279,7 +1277,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="48" customHeight="1">
+    <row r="22" ht="25" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>۱۷</t>
@@ -1311,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1">
+    <row r="23" ht="25" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
         <is>
           <t>۱۸</t>
@@ -1343,7 +1341,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="48" customHeight="1">
+    <row r="24" ht="25" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>۱۹</t>
@@ -1375,7 +1373,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1">
+    <row r="25" ht="25" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
         <is>
           <t>۲۰</t>
@@ -1407,7 +1405,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
+    <row r="26" ht="16" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>۲۱</t>
@@ -1427,7 +1425,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
+    <row r="27" ht="16" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>۲۲</t>
@@ -1447,7 +1445,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
+    <row r="28" ht="25" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
           <t>۲۳</t>
@@ -1479,7 +1477,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
+    <row r="29" ht="25" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>۲۴</t>
@@ -1511,7 +1509,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="48" customHeight="1">
+    <row r="30" ht="25" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
           <t>۲۵</t>
@@ -1543,7 +1541,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="48" customHeight="1">
+    <row r="31" ht="25" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>۲۶</t>
@@ -1575,7 +1573,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="48" customHeight="1">
+    <row r="32" ht="25" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
           <t>۲۷</t>
@@ -1607,7 +1605,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="48" customHeight="1">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>۲۸</t>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
+    <row r="34" ht="25" customHeight="1">
       <c r="A34" s="14" t="inlineStr">
         <is>
           <t>۲۹</t>
@@ -1671,7 +1669,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
+    <row r="35" ht="16" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>۳۰</t>
@@ -1691,7 +1689,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="64" customHeight="1">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
           <t>۳۱</t>
@@ -1723,7 +1721,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="20" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
           <t>جمع ساعات کارکرد در ماه: ۱۸۵ ساعت و ۲۰ دقیقه</t>
@@ -1735,8 +1733,8 @@
       <c r="E37" s="23" t="n"/>
       <c r="F37" s="23" t="n"/>
     </row>
-    <row r="38" ht="10" customHeight="1"/>
-    <row r="39" ht="26" customHeight="1">
+    <row r="38" ht="4" customHeight="1"/>
+    <row r="39" ht="18" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
           <t>امضاء فرد</t>
@@ -1756,21 +1754,21 @@
       </c>
       <c r="F39" s="24" t="n"/>
     </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-    </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="25" t="n"/>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="25" t="n"/>
-      <c r="D41" s="25" t="n"/>
-      <c r="E41" s="25" t="n"/>
-      <c r="F41" s="25" t="n"/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1785,9 +1783,9 @@
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A39:B39"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.35" right="0.35" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.18" right="0.18" top="0.2" bottom="0.2" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;9 کارکرد مرداد ۱۴۰۵ ـ صفحه &amp;P از &amp;N</oddFooter>

--- a/karkard/output/کارکرد-مرداد-1405.xlsx
+++ b/karkard/output/کارکرد-مرداد-1405.xlsx
@@ -802,12 +802,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۸:۲۵</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>۱۱:۴۵</t>
+          <t>۱۲:۴۰</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>۱۵:۲۵</t>
+          <t>۱۶:۱۵</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۸:۳۰</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۰۵</t>
+          <t>۱۷:۰۰</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>۱۵:۵۰</t>
+          <t>۱۶:۴۰</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -937,7 +937,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="25" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>۶</t>
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۰۵</t>
+          <t>۰۹:۳۰</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۰۰</t>
+          <t>۱۸:۲۵</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ پایش میزان مشارکت و تعامل مخاطبان کانال‌های استانی؛ ثبت و تنظیم اطلاعات کلاس سواد رسانه‌ای در سامانه نسرا</t>
+          <t>پاسخگویی به سؤالات و درخواست‌های نواحی و به‌روزرسانی محتوای کانال‌ها در ایتا، روبیکا و تلگرام؛ پایش میزان مشارکت و تعامل مخاطبان کانال‌های استانی؛ ثبت و تنظیم اطلاعات کلاس سواد رسانه‌ای در سامانه نسرا؛ تجمیع و تکمیل گزارش کارکرد ماه تیر</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۴۵</t>
+          <t>۰۸:۵۵</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>۱۵:۵۵</t>
+          <t>۱۷:۰۵</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>۰۸:۱۰</t>
+          <t>۰۹:۰۰</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>۱۲:۱۵</t>
+          <t>۱۳:۰۵</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>۱۱:۱۰</t>
+          <t>۰۸:۱۵</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>۱۳:۲۵</t>
+          <t>۱۰:۳۰</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>۰۸:۱۰</t>
+          <t>۰۸:۳۰</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۳۵</t>
+          <t>۱۶:۵۵</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۵۰</t>
+          <t>۰۸:۰۰</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۱۰</t>
+          <t>۱۷:۲۰</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۸:۱۵</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>۱۵:۴۰</t>
+          <t>۱۶:۲۰</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۲۰</t>
+          <t>۰۸:۱۵</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۳۵</t>
+          <t>۱۷:۳۰</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۸:۰۰</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>۱۱:۵۵</t>
+          <t>۱۲:۳۰</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>۱۱:۰۰</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>۱۲:۱۵</t>
+          <t>۰۹:۴۰</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>۱:۱۵</t>
+          <t>۱:۲۰</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۲۵</t>
+          <t>۰۸:۳۵</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۵۰</t>
+          <t>۱۷:۰۰</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۲۰</t>
+          <t>۰۸:۰۰</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۰۰</t>
+          <t>۱۶:۴۰</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۳۵</t>
+          <t>۰۹:۱۰</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۳۵</t>
+          <t>۱۸:۱۰</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۲۰</t>
+          <t>۰۸:۵۵</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۱۰</t>
+          <t>۱۷:۴۵</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="25" customHeight="1">
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
           <t>۲۳</t>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>۰۹:۲۰</t>
+          <t>۰۸:۲۰</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>۱۱:۴۰</t>
+          <t>۱۰:۴۰</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی) ـ ارتباط با مسئولان فضای مجازی نواحی و هماهنگی انتشار محتوای مناسبتی؛ به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی (دورکاری)</t>
+          <t>جمعه (تعطیل هفتگی) ـ ارتباط با مسئولان فضای مجازی نواحی و هماهنگی انتشار محتوای مناسبتی (دورکاری)</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۵۵</t>
+          <t>۰۸:۵۰</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۱۰</t>
+          <t>۱۸:۰۵</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1522,17 +1522,17 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۴۵</t>
+          <t>۰۸:۲۵</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>۱۵:۴۵</t>
+          <t>۱۶:۲۰</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>۸:۰۰</t>
+          <t>۷:۵۵</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۴۵</t>
+          <t>۰۹:۰۰</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۴۰</t>
+          <t>۱۶:۵۵</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۹:۱۰</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۳۰</t>
+          <t>۱۸:۱۰</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>۰۷:۵۰</t>
+          <t>۰۸:۲۵</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>۱۵:۵۰</t>
+          <t>۱۶:۲۵</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>۰۷:۵۵</t>
+          <t>۰۹:۲۵</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>۱۱:۴۵</t>
+          <t>۱۳:۱۵</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>۰۷:۳۰</t>
+          <t>۰۹:۰۵</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>۱۶:۲۰</t>
+          <t>۱۷:۵۵</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">

--- a/karkard/output/کارکرد-مرداد-1405.xlsx
+++ b/karkard/output/کارکرد-مرداد-1405.xlsx
@@ -1785,7 +1785,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.18" right="0.18" top="0.2" bottom="0.2" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;9 کارکرد مرداد ۱۴۰۵ ـ صفحه &amp;P از &amp;N</oddFooter>

--- a/karkard/output/کارکرد-مرداد-1405.xlsx
+++ b/karkard/output/کارکرد-مرداد-1405.xlsx
@@ -73,7 +73,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -102,11 +102,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF4EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
@@ -263,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -313,15 +308,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -331,7 +317,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -807,12 +793,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>۱۲:۴۰</t>
+          <t>۱۳:۰۰</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>۴:۱۵</t>
+          <t>۴:۳۵</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -837,7 +823,7 @@
       <c r="E7" s="12" t="inlineStr"/>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی)</t>
+          <t>جمعه (تعطیل هفتگی ـ روز ۲ مرداد)</t>
         </is>
       </c>
     </row>
@@ -859,12 +845,12 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۱۵</t>
+          <t>۱۶:۴۵</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>۷:۵۵</t>
+          <t>۸:۲۵</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -891,12 +877,12 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۰۰</t>
+          <t>۱۷:۲۵</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>۸:۳۰</t>
+          <t>۸:۵۵</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -923,17 +909,17 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۴۰</t>
+          <t>۱۷:۰۰</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>۸:۲۰</t>
+          <t>۸:۴۰</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ برگزاری جلسه هماهنگی مجازی با رابطان سواد رسانه‌ای نواحی؛ تهیه بروشور آموزشی سواد رسانه‌ای ویژه مربیان ناحیه فلاورجان</t>
+          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ برگزاری جلسه هماهنگی مجازی با رابطان سواد رسانه‌ای نواحی؛ تهیه بروشور آموزشی سواد رسانه‌ای ویژه مربیان ناحیه شهرضا</t>
         </is>
       </c>
     </row>
@@ -955,12 +941,12 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>۱۸:۲۵</t>
+          <t>۱۸:۳۵</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>۸:۵۵</t>
+          <t>۹:۰۵</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -987,12 +973,12 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>۱۷:۰۵</t>
+          <t>۱۷:۱۵</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>۸:۱۰</t>
+          <t>۸:۲۰</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -1019,12 +1005,12 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>۱۳:۰۵</t>
+          <t>۱۳:۲۰</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>۴:۰۵</t>
+          <t>۴:۲۰</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -1034,34 +1020,22 @@
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>۹</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>جمعه</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>۰۸:۱۵</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>۱۰:۳۰</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>۲:۱۵</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>جمعه (تعطیل هفتگی) ـ پاسخگویی تلفنی به نواحی و پیگیری امور ضروری کانال‌ها (دورکاری)</t>
+      <c r="C14" s="12" t="inlineStr"/>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>جمعه (تعطیل هفتگی ـ روز ۹ مرداد)</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1057,12 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۵۵</t>
+          <t>۱۷:۰۰</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>۸:۲۵</t>
+          <t>۸:۳۰</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -1115,12 +1089,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۲۰</t>
+          <t>۱۷:۳۰</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>۹:۲۰</t>
+          <t>۹:۳۰</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -1147,12 +1121,12 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۲۰</t>
+          <t>۱۶:۴۵</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>۸:۰۵</t>
+          <t>۸:۳۰</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
@@ -1177,7 +1151,7 @@
       <c r="E18" s="12" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>تعطیل رسمی (اربعین حسینی)</t>
+          <t>تعطیل رسمی (اربعین حسینی) ـ روز ۱۳ مرداد</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1173,12 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۳۰</t>
+          <t>۱۸:۰۰</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>۹:۱۵</t>
+          <t>۹:۴۵</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -1246,34 +1220,22 @@
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>۱۶</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>جمعه</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>۰۸:۲۰</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>۰۹:۴۰</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>۱:۲۰</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>جمعه (تعطیل هفتگی) ـ انتشار محتوای مناسبتی در کانال‌های استانی و پاسخگویی به مخاطبان (دورکاری)</t>
+      <c r="C21" s="12" t="inlineStr"/>
+      <c r="D21" s="12" t="inlineStr"/>
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>جمعه (تعطیل هفتگی ـ روز ۱۶ مرداد)</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1257,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>۱۷:۰۰</t>
+          <t>۱۷:۲۵</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>۸:۲۵</t>
+          <t>۸:۵۰</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -1327,12 +1289,12 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۴۰</t>
+          <t>۱۶:۵۰</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>۸:۴۰</t>
+          <t>۸:۵۰</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
@@ -1359,12 +1321,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>۱۸:۱۰</t>
+          <t>۱۸:۲۵</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>۹:۰۰</t>
+          <t>۹:۱۵</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -1391,17 +1353,17 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>۱۷:۴۵</t>
+          <t>۱۸:۰۵</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>۸:۵۰</t>
+          <t>۹:۱۰</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ پیگیری تشکیل و فعال‌سازی تیم تولید محتوای ناحیه هرند؛ بررسی گزارش‌های ارسالی ناحیه تیران و کرون و رفع اشکال موارد ناقص</t>
+          <t>رصد و به‌روزرسانی روزانه کانال‌های ایتا، روبیکا و تلگرام و پیگیری پیام‌های نواحی؛ پیگیری تشکیل و فعال‌سازی تیم تولید محتوای ناحیه مبارکه؛ بررسی گزارش‌های ارسالی ناحیه تیران و کرون و رفع اشکال موارد ناقص</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1383,7 @@
       <c r="E26" s="12" t="inlineStr"/>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>تعطیل رسمی (رحلت رسول اکرم (ص) و شهادت امام حسن مجتبی (ع))</t>
+          <t>تعطیل رسمی (رحلت رسول اکرم (ص) و شهادت امام حسن مجتبی (ع)) ـ روز ۲۱ مرداد</t>
         </is>
       </c>
     </row>
@@ -1441,39 +1403,27 @@
       <c r="E27" s="12" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>تعطیل رسمی (شهادت امام رضا (ع))</t>
+          <t>تعطیل رسمی (شهادت امام رضا (ع)) ـ روز ۲۲ مرداد</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>۲۳</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>جمعه</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>۰۸:۲۰</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>۱۰:۴۰</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>۲:۲۰</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>جمعه (تعطیل هفتگی) ـ ارتباط با مسئولان فضای مجازی نواحی و هماهنگی انتشار محتوای مناسبتی (دورکاری)</t>
+      <c r="C28" s="12" t="inlineStr"/>
+      <c r="D28" s="12" t="inlineStr"/>
+      <c r="E28" s="12" t="inlineStr"/>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>جمعه (تعطیل هفتگی ـ روز ۲۳ مرداد)</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1445,12 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>۱۸:۰۵</t>
+          <t>۱۸:۳۰</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>۹:۱۵</t>
+          <t>۹:۴۰</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
@@ -1527,17 +1477,17 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>۱۶:۲۰</t>
+          <t>۱۶:۳۰</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>۷:۵۵</t>
+          <t>۸:۰۵</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ به‌روزرسانی بخش سنجاق‌شده کانال و انتشار اطلاعیه‌های جدید ناحیه ورزنه؛ طراحی پوستر و اینفوگرافیک آموزشی برای انتشار در کانال استان</t>
+          <t>به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام و پاسخگویی به سؤالات نواحی؛ به‌روزرسانی بخش سنجاق‌شده کانال و انتشار اطلاعیه‌های جدید ناحیه لنجان؛ طراحی پوستر و اینفوگرافیک آموزشی برای انتشار در کانال استان</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1541,12 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>۱۸:۱۰</t>
+          <t>۱۸:۲۰</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>۹:۰۰</t>
+          <t>۹:۱۰</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -1623,12 +1573,12 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>۱۶:۲۵</t>
+          <t>۱۶:۳۰</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>۸:۰۰</t>
+          <t>۸:۰۵</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -1655,12 +1605,12 @@
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>۱۳:۱۵</t>
+          <t>۱۳:۲۵</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>۳:۵۰</t>
+          <t>۴:۰۰</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -1685,74 +1635,74 @@
       <c r="E35" s="12" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>جمعه (تعطیل هفتگی) ـ مصادف با تعطیل رسمی (شهادت امام حسن عسکری (ع))</t>
+          <t>جمعه (تعطیل هفتگی ـ روز ۳۰ مرداد) ـ مصادف با تعطیل رسمی (شهادت امام حسن عسکری (ع))</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>۳۱</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>شنبه</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>۰۹:۰۵</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>۱۷:۵۵</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>۸:۵۰</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="inlineStr">
-        <is>
-          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ بررسی نهایی مستندات ماه جاری و بستن پرونده گزارش ماهانه؛ ارتباط با مسئول نسرا در ناحیه شهرضا و پیگیری روند اجرای برنامه‌های آموزشی؛ پایش روزانه هشتگ‌ها و پویش‌های فضای مجازی مرتبط با سواد رسانه‌ای</t>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>۱۸:۲۰</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>۹:۱۵</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>پایش روزانه فضای مجازی نواحی و به‌روزرسانی کانال‌های ایتا، روبیکا و تلگرام؛ بررسی نهایی مستندات ماه جاری و بستن پرونده گزارش ماهانه؛ ارتباط با مسئول نسرا در ناحیه شاهین شهر و پیگیری روند اجرای برنامه‌های آموزشی؛ پایش روزانه هشتگ‌ها و پویش‌های فضای مجازی مرتبط با سواد رسانه‌ای</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>جمع ساعات کارکرد در ماه: ۱۸۵ ساعت و ۲۰ دقیقه</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="23" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="20" t="n"/>
     </row>
     <row r="38" ht="4" customHeight="1"/>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>امضاء فرد</t>
         </is>
       </c>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>امضاء مسئول مرکز فضای مجازی</t>
         </is>
       </c>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>تأیید مرکز فضای مجازی بسیج استان</t>
         </is>
       </c>
-      <c r="F39" s="24" t="n"/>
+      <c r="F39" s="21" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="4" t="n"/>
